--- a/reports/archive/weekly/shadow_report_weekly_2026-07-10.xlsx
+++ b/reports/archive/weekly/shadow_report_weekly_2026-07-10.xlsx
@@ -552,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>This week: 2026-W28  |  Last week: 2026-W27  |  Generated: 2026-07-10 00:01 IST</t>
+          <t>This week: 2026-W28  |  Last week: 2026-W27  |  Generated: 2026-07-10 13:14 IST</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>n=8  WR=0%</t>
+          <t>n=12  WR=0%</t>
         </is>
       </c>
     </row>
@@ -1090,11 +1090,11 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>pending (n=8)</t>
+          <t>pending (n=12)</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O122"/>
+  <dimension ref="A1:O126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -8732,6 +8732,250 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B123" s="13" t="inlineStr">
+        <is>
+          <t>DLF.NS</t>
+        </is>
+      </c>
+      <c r="C123" s="13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D123" s="13" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="E123" s="13" t="inlineStr">
+        <is>
+          <t>TRANSITION</t>
+        </is>
+      </c>
+      <c r="F123" s="13" t="inlineStr">
+        <is>
+          <t>37.5</t>
+        </is>
+      </c>
+      <c r="G123" s="13" t="inlineStr">
+        <is>
+          <t>687.75</t>
+        </is>
+      </c>
+      <c r="H123" s="13" t="inlineStr">
+        <is>
+          <t>722.14</t>
+        </is>
+      </c>
+      <c r="I123" s="13" t="inlineStr">
+        <is>
+          <t>667.12</t>
+        </is>
+      </c>
+      <c r="J123" s="13" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K123" s="13" t="inlineStr"/>
+      <c r="L123" s="13" t="inlineStr"/>
+      <c r="M123" s="13" t="inlineStr"/>
+      <c r="N123" s="13" t="inlineStr"/>
+      <c r="O123" s="13" t="inlineStr">
+        <is>
+          <t>skip:REGIME_CHOP_NO_BREAKOUT(TRANSITION/OTHER</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B124" s="13" t="inlineStr">
+        <is>
+          <t>HFCL.NS</t>
+        </is>
+      </c>
+      <c r="C124" s="13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D124" s="13" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="E124" s="13" t="inlineStr">
+        <is>
+          <t>TRANSITION</t>
+        </is>
+      </c>
+      <c r="F124" s="13" t="inlineStr">
+        <is>
+          <t>35.9</t>
+        </is>
+      </c>
+      <c r="G124" s="13" t="inlineStr">
+        <is>
+          <t>218.08</t>
+        </is>
+      </c>
+      <c r="H124" s="13" t="inlineStr">
+        <is>
+          <t>228.98</t>
+        </is>
+      </c>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>211.54</t>
+        </is>
+      </c>
+      <c r="J124" s="13" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K124" s="13" t="inlineStr"/>
+      <c r="L124" s="13" t="inlineStr"/>
+      <c r="M124" s="13" t="inlineStr"/>
+      <c r="N124" s="13" t="inlineStr"/>
+      <c r="O124" s="13" t="inlineStr">
+        <is>
+          <t>skip:REGIME_CHOP_NO_BREAKOUT(TRANSITION/OTHER</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B125" s="13" t="inlineStr">
+        <is>
+          <t>AVANTEL.NS</t>
+        </is>
+      </c>
+      <c r="C125" s="13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D125" s="13" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="E125" s="13" t="inlineStr">
+        <is>
+          <t>TRANSITION</t>
+        </is>
+      </c>
+      <c r="F125" s="13" t="inlineStr">
+        <is>
+          <t>62.0</t>
+        </is>
+      </c>
+      <c r="G125" s="13" t="inlineStr">
+        <is>
+          <t>178.92</t>
+        </is>
+      </c>
+      <c r="H125" s="13" t="inlineStr">
+        <is>
+          <t>187.87</t>
+        </is>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>173.55</t>
+        </is>
+      </c>
+      <c r="J125" s="13" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K125" s="13" t="inlineStr"/>
+      <c r="L125" s="13" t="inlineStr"/>
+      <c r="M125" s="13" t="inlineStr"/>
+      <c r="N125" s="13" t="inlineStr"/>
+      <c r="O125" s="13" t="inlineStr">
+        <is>
+          <t>skip:REGIME_CHOP_NO_BREAKOUT(TRANSITION/OTHER</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B126" s="13" t="inlineStr">
+        <is>
+          <t>EMBDL.NS</t>
+        </is>
+      </c>
+      <c r="C126" s="13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D126" s="13" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="E126" s="13" t="inlineStr">
+        <is>
+          <t>TRANSITION</t>
+        </is>
+      </c>
+      <c r="F126" s="13" t="inlineStr">
+        <is>
+          <t>73.7</t>
+        </is>
+      </c>
+      <c r="G126" s="13" t="inlineStr">
+        <is>
+          <t>64.10</t>
+        </is>
+      </c>
+      <c r="H126" s="13" t="inlineStr">
+        <is>
+          <t>67.30</t>
+        </is>
+      </c>
+      <c r="I126" s="13" t="inlineStr">
+        <is>
+          <t>62.18</t>
+        </is>
+      </c>
+      <c r="J126" s="13" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K126" s="13" t="inlineStr"/>
+      <c r="L126" s="13" t="inlineStr"/>
+      <c r="M126" s="13" t="inlineStr"/>
+      <c r="N126" s="13" t="inlineStr"/>
+      <c r="O126" s="13" t="inlineStr">
+        <is>
+          <t>skip:REGIME_CHOP_NO_BREAKOUT(TRANSITION/OTHER</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>

--- a/reports/archive/weekly/shadow_report_weekly_2026-07-10.xlsx
+++ b/reports/archive/weekly/shadow_report_weekly_2026-07-10.xlsx
@@ -552,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>This week: 2026-W28  |  Last week: 2026-W27  |  Generated: 2026-07-10 13:14 IST</t>
+          <t>This week: 2026-W28  |  Last week: 2026-W27  |  Generated: 2026-07-10 00:01 IST</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>n=12  WR=0%</t>
+          <t>n=8  WR=0%</t>
         </is>
       </c>
     </row>
@@ -1090,11 +1090,11 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>pending (n=12)</t>
+          <t>pending (n=8)</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O126"/>
+  <dimension ref="A1:O122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -8732,250 +8732,6 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="13" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="B123" s="13" t="inlineStr">
-        <is>
-          <t>DLF.NS</t>
-        </is>
-      </c>
-      <c r="C123" s="13" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D123" s="13" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="E123" s="13" t="inlineStr">
-        <is>
-          <t>TRANSITION</t>
-        </is>
-      </c>
-      <c r="F123" s="13" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
-      <c r="G123" s="13" t="inlineStr">
-        <is>
-          <t>687.75</t>
-        </is>
-      </c>
-      <c r="H123" s="13" t="inlineStr">
-        <is>
-          <t>722.14</t>
-        </is>
-      </c>
-      <c r="I123" s="13" t="inlineStr">
-        <is>
-          <t>667.12</t>
-        </is>
-      </c>
-      <c r="J123" s="13" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K123" s="13" t="inlineStr"/>
-      <c r="L123" s="13" t="inlineStr"/>
-      <c r="M123" s="13" t="inlineStr"/>
-      <c r="N123" s="13" t="inlineStr"/>
-      <c r="O123" s="13" t="inlineStr">
-        <is>
-          <t>skip:REGIME_CHOP_NO_BREAKOUT(TRANSITION/OTHER</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="13" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="B124" s="13" t="inlineStr">
-        <is>
-          <t>HFCL.NS</t>
-        </is>
-      </c>
-      <c r="C124" s="13" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D124" s="13" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="E124" s="13" t="inlineStr">
-        <is>
-          <t>TRANSITION</t>
-        </is>
-      </c>
-      <c r="F124" s="13" t="inlineStr">
-        <is>
-          <t>35.9</t>
-        </is>
-      </c>
-      <c r="G124" s="13" t="inlineStr">
-        <is>
-          <t>218.08</t>
-        </is>
-      </c>
-      <c r="H124" s="13" t="inlineStr">
-        <is>
-          <t>228.98</t>
-        </is>
-      </c>
-      <c r="I124" s="13" t="inlineStr">
-        <is>
-          <t>211.54</t>
-        </is>
-      </c>
-      <c r="J124" s="13" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K124" s="13" t="inlineStr"/>
-      <c r="L124" s="13" t="inlineStr"/>
-      <c r="M124" s="13" t="inlineStr"/>
-      <c r="N124" s="13" t="inlineStr"/>
-      <c r="O124" s="13" t="inlineStr">
-        <is>
-          <t>skip:REGIME_CHOP_NO_BREAKOUT(TRANSITION/OTHER</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="13" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="B125" s="13" t="inlineStr">
-        <is>
-          <t>AVANTEL.NS</t>
-        </is>
-      </c>
-      <c r="C125" s="13" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D125" s="13" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="E125" s="13" t="inlineStr">
-        <is>
-          <t>TRANSITION</t>
-        </is>
-      </c>
-      <c r="F125" s="13" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
-      </c>
-      <c r="G125" s="13" t="inlineStr">
-        <is>
-          <t>178.92</t>
-        </is>
-      </c>
-      <c r="H125" s="13" t="inlineStr">
-        <is>
-          <t>187.87</t>
-        </is>
-      </c>
-      <c r="I125" s="13" t="inlineStr">
-        <is>
-          <t>173.55</t>
-        </is>
-      </c>
-      <c r="J125" s="13" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K125" s="13" t="inlineStr"/>
-      <c r="L125" s="13" t="inlineStr"/>
-      <c r="M125" s="13" t="inlineStr"/>
-      <c r="N125" s="13" t="inlineStr"/>
-      <c r="O125" s="13" t="inlineStr">
-        <is>
-          <t>skip:REGIME_CHOP_NO_BREAKOUT(TRANSITION/OTHER</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="13" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="B126" s="13" t="inlineStr">
-        <is>
-          <t>EMBDL.NS</t>
-        </is>
-      </c>
-      <c r="C126" s="13" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D126" s="13" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="E126" s="13" t="inlineStr">
-        <is>
-          <t>TRANSITION</t>
-        </is>
-      </c>
-      <c r="F126" s="13" t="inlineStr">
-        <is>
-          <t>73.7</t>
-        </is>
-      </c>
-      <c r="G126" s="13" t="inlineStr">
-        <is>
-          <t>64.10</t>
-        </is>
-      </c>
-      <c r="H126" s="13" t="inlineStr">
-        <is>
-          <t>67.30</t>
-        </is>
-      </c>
-      <c r="I126" s="13" t="inlineStr">
-        <is>
-          <t>62.18</t>
-        </is>
-      </c>
-      <c r="J126" s="13" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K126" s="13" t="inlineStr"/>
-      <c r="L126" s="13" t="inlineStr"/>
-      <c r="M126" s="13" t="inlineStr"/>
-      <c r="N126" s="13" t="inlineStr"/>
-      <c r="O126" s="13" t="inlineStr">
-        <is>
-          <t>skip:REGIME_CHOP_NO_BREAKOUT(TRANSITION/OTHER</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>

--- a/reports/archive/weekly/shadow_report_weekly_2026-07-10.xlsx
+++ b/reports/archive/weekly/shadow_report_weekly_2026-07-10.xlsx
@@ -552,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>This week: 2026-W28  |  Last week: 2026-W27  |  Generated: 2026-07-10 00:01 IST</t>
+          <t>This week: 2026-W28  |  Last week: 2026-W27  |  Generated: 2026-07-10 19:00 IST</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>n=8  WR=0%</t>
+          <t>n=10  WR=0%</t>
         </is>
       </c>
     </row>
@@ -1090,11 +1090,11 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>pending (n=8)</t>
+          <t>pending (n=10)</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O122"/>
+  <dimension ref="A1:O124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -8732,6 +8732,128 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B123" s="13" t="inlineStr">
+        <is>
+          <t>DLF.NS</t>
+        </is>
+      </c>
+      <c r="C123" s="13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D123" s="13" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="E123" s="13" t="inlineStr">
+        <is>
+          <t>TRANSITION</t>
+        </is>
+      </c>
+      <c r="F123" s="13" t="inlineStr">
+        <is>
+          <t>61.4</t>
+        </is>
+      </c>
+      <c r="G123" s="13" t="inlineStr">
+        <is>
+          <t>685.75</t>
+        </is>
+      </c>
+      <c r="H123" s="13" t="inlineStr">
+        <is>
+          <t>720.04</t>
+        </is>
+      </c>
+      <c r="I123" s="13" t="inlineStr">
+        <is>
+          <t>665.18</t>
+        </is>
+      </c>
+      <c r="J123" s="13" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K123" s="13" t="inlineStr"/>
+      <c r="L123" s="13" t="inlineStr"/>
+      <c r="M123" s="13" t="inlineStr"/>
+      <c r="N123" s="13" t="inlineStr"/>
+      <c r="O123" s="13" t="inlineStr">
+        <is>
+          <t>skip:REGIME_CHOP_NO_BREAKOUT(TRANSITION/OTHER</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B124" s="13" t="inlineStr">
+        <is>
+          <t>RISHABH.NS</t>
+        </is>
+      </c>
+      <c r="C124" s="13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D124" s="13" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="E124" s="13" t="inlineStr">
+        <is>
+          <t>TRANSITION</t>
+        </is>
+      </c>
+      <c r="F124" s="13" t="inlineStr">
+        <is>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="G124" s="13" t="inlineStr">
+        <is>
+          <t>662.10</t>
+        </is>
+      </c>
+      <c r="H124" s="13" t="inlineStr">
+        <is>
+          <t>695.21</t>
+        </is>
+      </c>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>642.24</t>
+        </is>
+      </c>
+      <c r="J124" s="13" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K124" s="13" t="inlineStr"/>
+      <c r="L124" s="13" t="inlineStr"/>
+      <c r="M124" s="13" t="inlineStr"/>
+      <c r="N124" s="13" t="inlineStr"/>
+      <c r="O124" s="13" t="inlineStr">
+        <is>
+          <t>skip:REGIME_CHOP_NO_BREAKOUT(TRANSITION/OTHER</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
